--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint 3/plantilla_burndown.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint 3/plantilla_burndown.xlsx
@@ -569,33 +569,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 3 - FitSearch'!$B$38:$P$38</c:f>
+              <c:f>'Sprint 3 - FitSearch'!$B$39:$P$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>97</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>71</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>65</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>51</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>33</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>2</c:v>
@@ -716,51 +716,51 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 3 - FitSearch'!$B$40:$P$40</c:f>
+              <c:f>'Sprint 3 - FitSearch'!$B$41:$P$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>97</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.0714</c:v>
+                  <c:v>60.3571</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>83.1429</c:v>
+                  <c:v>55.7143</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>76.2143</c:v>
+                  <c:v>51.0714</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>69.2857</c:v>
+                  <c:v>46.4286</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>62.3571</c:v>
+                  <c:v>41.7857</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>55.4286</c:v>
+                  <c:v>37.1429</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>48.5</c:v>
+                  <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41.5714</c:v>
+                  <c:v>27.8571</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>34.6429</c:v>
+                  <c:v>23.2143</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>27.7143</c:v>
+                  <c:v>18.5714</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.7857</c:v>
+                  <c:v>13.9286</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13.8571</c:v>
+                  <c:v>9.2857</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.9286</c:v>
+                  <c:v>4.6429</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -990,13 +990,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -1196,7 +1196,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="70"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -1325,7 +1325,7 @@
       <c r="P5" s="10"/>
       <c r="Q5" s="15" t="n">
         <f aca="false">SUM(C5:P5)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1343,11 +1343,9 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="I6" s="10"/>
       <c r="J6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
@@ -1357,7 +1355,7 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="15" t="n">
         <f aca="false">SUM(C6:P6)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1375,10 +1373,10 @@
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
-      <c r="I7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
@@ -1397,7 +1395,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -1406,11 +1404,9 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
@@ -1419,7 +1415,7 @@
       <c r="P8" s="10"/>
       <c r="Q8" s="15" t="n">
         <f aca="false">SUM(C8:P8)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1429,7 +1425,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -1438,11 +1434,9 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
@@ -1451,7 +1445,7 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="15" t="n">
         <f aca="false">SUM(C9:P9)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1461,7 +1455,7 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -1469,9 +1463,7 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="I10" s="10"/>
       <c r="J10" s="10" t="n">
         <v>1</v>
       </c>
@@ -1483,7 +1475,7 @@
       <c r="P10" s="10"/>
       <c r="Q10" s="15" t="n">
         <f aca="false">SUM(C10:P10)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1493,10 +1485,10 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -1513,7 +1505,7 @@
       <c r="P11" s="10"/>
       <c r="Q11" s="15" t="n">
         <f aca="false">SUM(C11:P11)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1523,10 +1515,10 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -1543,7 +1535,7 @@
       <c r="P12" s="10"/>
       <c r="Q12" s="15" t="n">
         <f aca="false">SUM(C12:P12)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1553,10 +1545,10 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -1573,7 +1565,7 @@
       <c r="P13" s="10"/>
       <c r="Q13" s="15" t="n">
         <f aca="false">SUM(C13:P13)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1583,10 +1575,10 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -1603,7 +1595,7 @@
       <c r="P14" s="10"/>
       <c r="Q14" s="15" t="n">
         <f aca="false">SUM(C14:P14)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1613,10 +1605,10 @@
         </is>
       </c>
       <c r="B15" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1633,7 +1625,7 @@
       <c r="P15" s="10"/>
       <c r="Q15" s="15" t="n">
         <f aca="false">SUM(C15:P15)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1643,10 +1635,10 @@
         </is>
       </c>
       <c r="B16" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -1663,7 +1655,7 @@
       <c r="P16" s="10"/>
       <c r="Q16" s="15" t="n">
         <f aca="false">SUM(C16:P16)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1673,10 +1665,10 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -1693,7 +1685,7 @@
       <c r="P17" s="10"/>
       <c r="Q17" s="15" t="n">
         <f aca="false">SUM(C17:P17)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1703,10 +1695,10 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
@@ -1723,7 +1715,7 @@
       <c r="P18" s="10"/>
       <c r="Q18" s="15" t="n">
         <f aca="false">SUM(C18:P18)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1733,10 +1725,10 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -1753,7 +1745,7 @@
       <c r="P19" s="10"/>
       <c r="Q19" s="15" t="n">
         <f aca="false">SUM(C19:P19)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1791,7 +1783,7 @@
         </is>
       </c>
       <c r="B21" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -1800,11 +1792,9 @@
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
@@ -1813,7 +1803,7 @@
       <c r="P21" s="10"/>
       <c r="Q21" s="15" t="n">
         <f aca="false">SUM(C21:P21)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1823,7 +1813,7 @@
         </is>
       </c>
       <c r="B22" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -1834,9 +1824,7 @@
       <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
@@ -1845,7 +1833,7 @@
       <c r="P22" s="10"/>
       <c r="Q22" s="15" t="n">
         <f aca="false">SUM(C22:P22)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1885,7 +1873,7 @@
         </is>
       </c>
       <c r="B24" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -1893,7 +1881,7 @@
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
@@ -1905,7 +1893,7 @@
       <c r="P24" s="10"/>
       <c r="Q24" s="15" t="n">
         <f aca="false">SUM(C24:P24)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,15 +1935,15 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
@@ -1969,7 +1957,7 @@
       <c r="P26" s="10"/>
       <c r="Q26" s="15" t="n">
         <f aca="false">SUM(C26:P26)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1979,16 +1967,14 @@
         </is>
       </c>
       <c r="B27" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
@@ -2001,7 +1987,7 @@
       <c r="P27" s="10"/>
       <c r="Q27" s="15" t="n">
         <f aca="false">SUM(C27:P27)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2041,7 +2027,7 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -2051,7 +2037,7 @@
         <v>3</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>1</v>
@@ -2065,7 +2051,7 @@
       <c r="P29" s="10"/>
       <c r="Q29" s="15" t="n">
         <f aca="false">SUM(C29:P29)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2075,7 +2061,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -2083,7 +2069,7 @@
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
@@ -2095,24 +2081,24 @@
       <c r="P30" s="10"/>
       <c r="Q30" s="15" t="n">
         <f aca="false">SUM(C30:P30)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 3 — Documentar el flujo del profesional: DAS v1.15, casos CP-050 a CP-060, defectos 15 a 24 y capturas</t>
+          <t xml:space="preserve">Sprint 3 — Cerrar la documentación del Sprint 2: horas reales, burndown, Documento Sprint Backlog 2 y Documento Validando Sprint 2</t>
         </is>
       </c>
       <c r="B31" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
+      <c r="D31" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="E31" s="10"/>
-      <c r="F31" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
@@ -2125,36 +2111,28 @@
       <c r="P31" s="10"/>
       <c r="Q31" s="15" t="n">
         <f aca="false">SUM(C31:P31)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 3 — Revisar el código de los PR del Sprint 3 (#12, #14, #15, #19, #20, #21 y #22) antes de fusionarlos</t>
+          <t xml:space="preserve">Sprint 3 — Documentar el flujo del profesional: DAS v1.15, casos CP-050 a CP-060, defectos 15 a 24 y capturas</t>
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="10" t="n">
+      <c r="E32" s="10"/>
+      <c r="F32" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
       <c r="M32" s="10"/>
@@ -2163,28 +2141,36 @@
       <c r="P32" s="10"/>
       <c r="Q32" s="15" t="n">
         <f aca="false">SUM(C32:P32)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 3 — Estandarizar el tablero de Trello con una de las plantillas Scrum del docente (listas, etiquetas de sprint y épica, tarjetas de las historias)</t>
+          <t xml:space="preserve">Sprint 3 — Revisar el código de los PR del Sprint 3 (#12, #14, #15, #16, #19, #20, #21 y #22) antes de fusionarlos</t>
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10" t="n">
+      <c r="E33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
+      <c r="J33" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
       <c r="M33" s="10"/>
@@ -2193,30 +2179,28 @@
       <c r="P33" s="10"/>
       <c r="Q33" s="15" t="n">
         <f aca="false">SUM(C33:P33)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 3 — Actualizar el DAS (versiones 1.16 a 1.22), los diagramas del Sprint 3 y las exportaciones del tablero Miro</t>
+          <t xml:space="preserve">Sprint 3 — Estandarizar el tablero de Trello con una de las plantillas Scrum del docente (listas, etiquetas de sprint y épica, tarjetas de las historias)</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
+      <c r="F34" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="G34" s="10"/>
-      <c r="H34" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="H34" s="10"/>
       <c r="I34" s="10"/>
-      <c r="J34" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
@@ -2231,7 +2215,7 @@
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 3 — Corregir el límite de reservas para no contar las citas pasadas (defecto 26) y ajustes de la revisión del PR #22</t>
+          <t xml:space="preserve">Sprint 3 — Actualizar el DAS (versiones 1.16 a 1.22), los diagramas del Sprint 3 y las exportaciones del tablero Miro</t>
         </is>
       </c>
       <c r="B35" s="15" t="n">
@@ -2242,11 +2226,11 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="H35" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="I35" s="10"/>
-      <c r="J35" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
@@ -2255,29 +2239,27 @@
       <c r="P35" s="10"/>
       <c r="Q35" s="15" t="n">
         <f aca="false">SUM(C35:P35)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 3 — Documentación y sincronización: conciliación de backlogs, decisiones del PO, casos CP-069 a CP-080, defectos 25 y 26, Guía 2.4, control, Drive y Trello</t>
+          <t xml:space="preserve">Sprint 3 — Corregir el límite de reservas para no contar las citas pasadas (defecto 26) y ajustes de la revisión del PR #22</t>
         </is>
       </c>
       <c r="B36" s="15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
-      <c r="G36" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="G36" s="10"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="J36" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
@@ -2287,149 +2269,163 @@
       <c r="P36" s="10"/>
       <c r="Q36" s="15" t="n">
         <f aca="false">SUM(C36:P36)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23" t="inlineStr">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 3 — Documentación y sincronización: subida al Drive, conciliación de backlogs, decisiones del PO, casos CP-069 a CP-080, defectos 25 y 26, Guía 2.4, control y Trello</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="15" t="n">
+        <f aca="false">SUM(C37:P37)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Reales de producto por realizar</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <f aca="false">SUM(B5:B36)</f>
-        <v>97</v>
-      </c>
-      <c r="C38" s="15" t="n">
-        <f aca="false">B38-SUM(C5:C36)</f>
-        <v>71</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <f aca="false">C38-SUM(D5:D36)</f>
-        <v>71</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <f aca="false">D38-SUM(E5:E36)</f>
+      <c r="B39" s="3" t="n">
+        <f aca="false">SUM(B5:B37)</f>
         <v>65</v>
       </c>
-      <c r="F38" s="15" t="n">
-        <f aca="false">E38-SUM(F5:F36)</f>
+      <c r="C39" s="15" t="n">
+        <f aca="false">B39-SUM(C5:C37)</f>
+        <v>55</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <f aca="false">C39-SUM(D5:D37)</f>
         <v>51</v>
       </c>
-      <c r="G38" s="15" t="n">
-        <f aca="false">F38-SUM(G5:G36)</f>
-        <v>45</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <f aca="false">G38-SUM(H5:H36)</f>
-        <v>33</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <f aca="false">H38-SUM(I5:I36)</f>
-        <v>21</v>
-      </c>
-      <c r="J38" s="15" t="n">
-        <f aca="false">I38-SUM(J5:J36)</f>
+      <c r="E39" s="15" t="n">
+        <f aca="false">D39-SUM(E5:E37)</f>
+        <v>42</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <f aca="false">E39-SUM(F5:F37)</f>
+        <v>34</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <f aca="false">F39-SUM(G5:G37)</f>
+        <v>27</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <f aca="false">G39-SUM(H5:H37)</f>
+        <v>20</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <f aca="false">H39-SUM(I5:I37)</f>
+        <v>12</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <f aca="false">I39-SUM(J5:J37)</f>
         <v>2</v>
       </c>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Estimadas de producto por realizar (línea ideal)</t>
         </is>
       </c>
-      <c r="B40" s="24" t="n">
-        <f aca="false">SUM(B5:B36)</f>
-        <v>97</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <f aca="false">B40-(SUM($B$5:$B$36)/14)</f>
-        <v>90.0714</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <f aca="false">C40-(SUM($B$5:$B$36)/14)</f>
-        <v>83.1429</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <f aca="false">D40-(SUM($B$5:$B$36)/14)</f>
-        <v>76.2143</v>
-      </c>
-      <c r="F40" s="15" t="n">
-        <f aca="false">E40-(SUM($B$5:$B$36)/14)</f>
-        <v>69.2857</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <f aca="false">F40-(SUM($B$5:$B$36)/14)</f>
-        <v>62.3571</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <f aca="false">G40-(SUM($B$5:$B$36)/14)</f>
-        <v>55.4286</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <f aca="false">H40-(SUM($B$5:$B$36)/14)</f>
-        <v>48.5</v>
-      </c>
-      <c r="J40" s="15" t="n">
-        <f aca="false">I40-(SUM($B$5:$B$36)/14)</f>
-        <v>41.5714</v>
-      </c>
-      <c r="K40" s="15" t="n">
-        <f aca="false">J40-(SUM($B$5:$B$36)/14)</f>
-        <v>34.6429</v>
-      </c>
-      <c r="L40" s="15" t="n">
-        <f aca="false">K40-(SUM($B$5:$B$36)/14)</f>
-        <v>27.7143</v>
-      </c>
-      <c r="M40" s="15" t="n">
-        <f aca="false">L40-(SUM($B$5:$B$36)/14)</f>
-        <v>20.7857</v>
-      </c>
-      <c r="N40" s="15" t="n">
-        <f aca="false">M40-(SUM($B$5:$B$36)/14)</f>
-        <v>13.8571</v>
-      </c>
-      <c r="O40" s="15" t="n">
-        <f aca="false">N40-(SUM($B$5:$B$36)/14)</f>
-        <v>6.9286</v>
-      </c>
-      <c r="P40" s="15" t="n">
-        <f aca="false">O40-(SUM($B$5:$B$36)/14)</f>
+      <c r="B41" s="24" t="n">
+        <f aca="false">SUM(B5:B37)</f>
+        <v>65</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <f aca="false">B41-(SUM($B$5:$B$37)/14)</f>
+        <v>60.3571</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <f aca="false">C41-(SUM($B$5:$B$37)/14)</f>
+        <v>55.7143</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <f aca="false">D41-(SUM($B$5:$B$37)/14)</f>
+        <v>51.0714</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <f aca="false">E41-(SUM($B$5:$B$37)/14)</f>
+        <v>46.4286</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <f aca="false">F41-(SUM($B$5:$B$37)/14)</f>
+        <v>41.7857</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <f aca="false">G41-(SUM($B$5:$B$37)/14)</f>
+        <v>37.1429</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <f aca="false">H41-(SUM($B$5:$B$37)/14)</f>
+        <v>32.5</v>
+      </c>
+      <c r="J41" s="15" t="n">
+        <f aca="false">I41-(SUM($B$5:$B$37)/14)</f>
+        <v>27.8571</v>
+      </c>
+      <c r="K41" s="15" t="n">
+        <f aca="false">J41-(SUM($B$5:$B$37)/14)</f>
+        <v>23.2143</v>
+      </c>
+      <c r="L41" s="15" t="n">
+        <f aca="false">K41-(SUM($B$5:$B$37)/14)</f>
+        <v>18.5714</v>
+      </c>
+      <c r="M41" s="15" t="n">
+        <f aca="false">L41-(SUM($B$5:$B$37)/14)</f>
+        <v>13.9286</v>
+      </c>
+      <c r="N41" s="15" t="n">
+        <f aca="false">M41-(SUM($B$5:$B$37)/14)</f>
+        <v>9.2857</v>
+      </c>
+      <c r="O41" s="15" t="n">
+        <f aca="false">N41-(SUM($B$5:$B$37)/14)</f>
+        <v>4.6429</v>
+      </c>
+      <c r="P41" s="15" t="n">
+        <f aca="false">O41-(SUM($B$5:$B$37)/14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nota: burndown del Sprint 3 (semanas 9 y 10, del 05-10-2026 al 18-10-2026; día 1 = 05-10-2026), con el avance al 12-10-2026 (día 8). 32 tareas con 97 h estimadas. Horas registradas el 12-10-2026 según el trabajo entregado en GitHub (commits, pull requests y revisiones de cada integrante): Rodrigo Cárcamo Rojas 52 h, Luis Méndez 40 h y Nicolás Silva 3 h (95 h en total). Las tareas de FS-HU-05 y FS-HU-21 a FS-HU-24 se implementaron el 03-10-2026, antes del inicio, y se registran en el día 1. Quedan 2 h: CP-078 con el mapa real sobre main y los marcos de Miro del DAS 1.22.</t>
-        </is>
-      </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-    </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="26"/>
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota: burndown del Sprint 3 (semanas 9 y 10, del 05-10-2026 al 18-10-2026; día 1 = 05-10-2026), con el avance al 12-10-2026 (día 8). 33 tareas con 65 h estimadas. Horas registradas el 12-10-2026 según el trabajo entregado en GitHub (commits, pull requests y revisiones de cada integrante), con un máximo de 5 h por persona y día: Rodrigo Cárcamo Rojas 37 h, Luis Méndez 23 h y Nicolás Silva 3 h (63 h en total). Las tareas de FS-HU-05 y FS-HU-21 a FS-HU-24 se implementaron el 02 y 03-10-2026, antes del inicio (10 h), y se registran en el día 1. Quedan 2 h: CP-078 con el mapa real sobre main y los marcos de Miro del DAS 1.22.</t>
+        </is>
+      </c>
       <c r="B43" s="26"/>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -2482,12 +2478,30 @@
       <c r="O45" s="26"/>
       <c r="P45" s="26"/>
     </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="26"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:P3"/>
-    <mergeCell ref="A42:P45"/>
+    <mergeCell ref="A43:P46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
